--- a/planning.xlsx
+++ b/planning.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\chargou\Opencode\L3-Info-EDT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B04F331-2CBB-4CC1-8631-D5ECDC2B802E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E66BD00-72A3-47D8-8717-4F68CB4152D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Evenements" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3094" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3094" uniqueCount="507">
   <si>
     <t>Date du Lundi de début de semaine</t>
   </si>
@@ -1536,6 +1536,12 @@
   </si>
   <si>
     <t>https://ecampus.paris-saclay.fr/course/view.php?id=206287#section-39</t>
+  </si>
+  <si>
+    <t>14:00-18:15</t>
+  </si>
+  <si>
+    <t>14:00-17:45</t>
   </si>
 </sst>
 </file>
@@ -4690,7 +4696,7 @@
         <v>53</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>59</v>
+        <v>505</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>64</v>
@@ -7920,7 +7926,7 @@
         <v>53</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>59</v>
+        <v>505</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>64</v>
@@ -11133,7 +11139,7 @@
         <v>53</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>59</v>
+        <v>505</v>
       </c>
       <c r="D322" s="2" t="s">
         <v>64</v>
@@ -11278,7 +11284,7 @@
         <v>19</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>33</v>
+        <v>506</v>
       </c>
       <c r="D327" s="2" t="s">
         <v>64</v>
@@ -11539,7 +11545,7 @@
         <v>10</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>33</v>
+        <v>506</v>
       </c>
       <c r="D336" s="2" t="s">
         <v>64</v>
